--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
@@ -88,19 +88,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>LUGO</t>
+    <t>PRADO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>ZAYRA</t>
+    <t>ANETTE</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -699,16 +699,19 @@
         <v>10</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>10</v>
       </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -722,16 +725,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.12</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -745,16 +751,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -768,16 +777,19 @@
         <v>18</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -791,16 +803,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -814,16 +829,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H7">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -905,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>92.68000000000001</v>
+        <v>95.12</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -931,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -957,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -983,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1018,7 +1036,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -1060,7 +1078,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920100</v>
+        <v>22330051920098</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -1078,7 +1096,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -46,21 +46,18 @@
     <t>REALIZA MANTENIMIENTO PREVENTIVO</t>
   </si>
   <si>
+    <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
+  </si>
+  <si>
     <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
   </si>
   <si>
-    <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
-  </si>
-  <si>
     <t>CLASIFICA LOS ELEMENTOS BÁSICOS DE LA RED LAN</t>
   </si>
   <si>
     <t>3ASV</t>
   </si>
   <si>
-    <t>5ALCM</t>
-  </si>
-  <si>
     <t>5APM</t>
   </si>
   <si>
@@ -88,22 +85,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
   </si>
 </sst>
 </file>
@@ -461,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -527,48 +515,48 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>92.68000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -579,30 +567,30 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>94.44</v>
+        <v>92</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -611,41 +599,15 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>25</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
         <v>9.1</v>
       </c>
     </row>
@@ -656,7 +618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -722,48 +684,48 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>95.12</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -774,7 +736,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -783,65 +745,39 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>25</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>96</v>
-      </c>
-      <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -917,48 +853,48 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>95.12</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -969,7 +905,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -978,21 +914,21 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -1010,32 +946,6 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>25</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
         <v>9.4</v>
       </c>
     </row>
@@ -1046,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1055,39 +965,39 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920426</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1097,29 +1007,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920105</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
+    <t>MOISES ALBERTO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -567,10 +594,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -579,7 +606,7 @@
         <v>23</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>79.31</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -593,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -602,13 +629,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -736,10 +763,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -748,7 +775,7 @@
         <v>25</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -762,7 +789,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -771,13 +798,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -859,16 +886,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -894,7 +921,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,10 +932,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -917,7 +944,7 @@
         <v>25</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H5">
         <v>8.4</v>
@@ -931,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -940,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,25 +1015,94 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920426</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920305</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920309</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,42 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -597,19 +561,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>79.31</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -766,19 +730,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -935,19 +899,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -983,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1013,98 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920305</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920309</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920315</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
